--- a/data/official_data/knowledge/colleges.xlsx
+++ b/data/official_data/knowledge/colleges.xlsx
@@ -16,91 +16,360 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="26">
-  <si>
-    <t>Topic</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>LastUpdated</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>Constituent Colleges</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
   <si>
     <t>Overview</t>
   </si>
   <si>
-    <t>Cluster University Srinagar consists of constituent colleges offering undergraduate, postgraduate and professional programmes.</t>
-  </si>
-  <si>
-    <t>Official CUS Website</t>
-  </si>
-  <si>
     <t>Amar Singh College</t>
   </si>
   <si>
-    <t>Amar Singh College is a constituent college of Cluster University Srinagar.</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Gogji Bagh, Srinagar</t>
-  </si>
-  <si>
     <t>Constituent College</t>
   </si>
   <si>
     <t>Sri Pratap College</t>
   </si>
   <si>
-    <t>Sri Pratap College is a constituent college of Cluster University Srinagar.</t>
-  </si>
-  <si>
-    <t>M.A. Road, Srinagar</t>
-  </si>
-  <si>
     <t>Government College for Women</t>
   </si>
   <si>
-    <t>Government College for Women is a constituent college of Cluster University Srinagar.</t>
-  </si>
-  <si>
-    <t>Institute of Advanced Studies</t>
-  </si>
-  <si>
-    <t>Official Information</t>
-  </si>
-  <si>
-    <t>Institute of Advanced Studies is a constituent college of Cluster University Srinagar.</t>
-  </si>
-  <si>
-    <t>Students can visit the official university website for detailed information about constituent colleges and their programmes.</t>
-  </si>
-  <si>
-    <t>https://www.cusrinagar.edu.in</t>
+    <t>College Name</t>
+  </si>
+  <si>
+    <t>Short Name</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Established</t>
+  </si>
+  <si>
+    <t>Campus</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Principal</t>
+  </si>
+  <si>
+    <t>Departments</t>
+  </si>
+  <si>
+    <t>Programmes Offered</t>
+  </si>
+  <si>
+    <t>Library</t>
+  </si>
+  <si>
+    <t>Hostel</t>
+  </si>
+  <si>
+    <t>Laboratories</t>
+  </si>
+  <si>
+    <t>Sports</t>
+  </si>
+  <si>
+    <t>NSS</t>
+  </si>
+  <si>
+    <t>Facilities</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>Google Maps</t>
+  </si>
+  <si>
+    <t>NCC</t>
+  </si>
+  <si>
+    <t>SP College</t>
+  </si>
+  <si>
+    <t>Cluster University Srinagar</t>
+  </si>
+  <si>
+    <t>M.A. Road Campus</t>
+  </si>
+  <si>
+    <t>M.A. Road, Srinagar – 190001, Jammu &amp; Kashmir</t>
+  </si>
+  <si>
+    <t>Srinagar</t>
+  </si>
+  <si>
+    <t>Jammu &amp; Kashmir</t>
+  </si>
+  <si>
+    <t>Prof. (Dr.) Haris Izhar Tantray</t>
+  </si>
+  <si>
+    <t>Sri Pratap College is the oldest and one of the premier institutions of higher education in Kashmir. Established in 1905, it is a constituent college of Cluster University Srinagar offering undergraduate, postgraduate and integrated programmes with a strong focus on science education, research, innovation and holistic student development.</t>
+  </si>
+  <si>
+    <t>Biochemistry, Bioinformatics, Biotechnology, Botany, Chemistry, Clinical Biochemistry, Electronics, English, Environmental Studies, Geography, Geology, Human Genetics, Information Technology, Mathematics, Physics, Statistics, Water Management, Zoology</t>
+  </si>
+  <si>
+    <t>Undergraduate, Postgraduate and Integrated programmes in Science including Physics, Chemistry, Botany, Zoology, Biochemistry, Biotechnology, Environmental Science, Information Technology, Geography and related disciplines.</t>
+  </si>
+  <si>
+    <t>Central Library available</t>
+  </si>
+  <si>
+    <t>Boys Hostel available</t>
+  </si>
+  <si>
+    <t>Well-equipped science laboratories, Multidisciplinary Research Centre, Hydrobiology Research Centre, E-Content Recording Studio and other departmental laboratories.</t>
+  </si>
+  <si>
+    <t>Indoor and outdoor sports facilities available; college has a Sports Committee and Sports Policy.</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Smart classrooms, Central Library, Boys Hostel, Multidisciplinary Research Centre, Hydrobiology Research Centre, Browsing Centre, E-Content Recording Studio, Day Care Centre, Wi-Fi-enabled campus, Seminar Hall, Sports facilities.</t>
+  </si>
+  <si>
+    <t>https://spcollege.edu.in</t>
+  </si>
+  <si>
+    <t>https://maps.google.com/?q=Sri+Pratap+College+Srinagar</t>
+  </si>
+  <si>
+    <t>Official Email</t>
+  </si>
+  <si>
+    <t>sri-pratap-college@jk.gov.in</t>
+  </si>
+  <si>
+    <t>ASC</t>
+  </si>
+  <si>
+    <t>1913 (Technical Institute); converted into Amar Singh College in 1942</t>
+  </si>
+  <si>
+    <t>Gogji Bagh Campus</t>
+  </si>
+  <si>
+    <t>Gogji Bagh, Srinagar – 190008, Jammu &amp; Kashmir</t>
+  </si>
+  <si>
+    <t>Prof. (Dr.) Tehmina Yousuf</t>
+  </si>
+  <si>
+    <t>Amar Singh College is one of the oldest and premier institutions of higher education in Kashmir. A constituent college of Cluster University Srinagar, it offers undergraduate, postgraduate and professional programmes with emphasis on academic excellence, research, innovation and holistic student development.</t>
+  </si>
+  <si>
+    <t>Arabic, Botany, Chemistry, Commerce, Computer Applications, Economics, Education, English, Environmental Science, Geography, Geology, History, Islamic Studies, Kashmiri, Mass Communication, Mathematics, Music, Persian, Philosophy, Physical Education, Physics, Political Science, Psychology, Public Administration, Sociology, Statistics, Tourism &amp; Travel Management, Urdu, Zoology, Anthropology.</t>
+  </si>
+  <si>
+    <t>Undergraduate, Postgraduate and Integrated programmes in Arts, Science, Commerce and Computer Applications, including postgraduate studies in Geography and various job-oriented certificate courses.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Central Library with over </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>70,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> books, including rare books.</t>
+    </r>
+  </si>
+  <si>
+    <t>Not Available</t>
+  </si>
+  <si>
+    <t>Well-equipped laboratories for Chemistry, Physics, Botany, Zoology, Geography, Geology, Environmental Science, Computer Applications and other science departments.</t>
+  </si>
+  <si>
+    <t>Indoor and outdoor sports facilities with Physical Education and sports activities.</t>
+  </si>
+  <si>
+    <t>Smart classrooms, Central Library, ICT facilities, seminar halls, auditorium, Wi-Fi campus, canteen, IGNOU Study Centre, career guidance, research facilities, NSS, NCC and sports infrastructure.</t>
+  </si>
+  <si>
+    <t>https://www.amarsinghcollege.ac.in</t>
+  </si>
+  <si>
+    <t>https://maps.google.com/?q=Amar+Singh+College+Srinagar</t>
+  </si>
+  <si>
+    <t>principal@amarsinghcollege.ac.in</t>
+  </si>
+  <si>
+    <t>Abdul Ahad Azad Memorial Degree College</t>
+  </si>
+  <si>
+    <t>1970 (academic session commenced in 1972)</t>
+  </si>
+  <si>
+    <t>Bemina Campus</t>
+  </si>
+  <si>
+    <t>Iqbal Abad, Bemina, Srinagar – 190018, Jammu &amp; Kashmir Abdul Ahad Azad Memorial Degree College Bemina</t>
+  </si>
+  <si>
+    <t>Prof. Muzafar Ahmad Bhat</t>
+  </si>
+  <si>
+    <t>Abdul Ahad Azad Memorial Degree College is one of the largest constituent colleges of Cluster University Srinagar. Established in 1970, the college offers undergraduate, postgraduate, integrated and professional programmes in Arts, Science, Commerce and Management. It is NAAC Grade A accredited and is known for its spacious campus, academic excellence, research, and holistic student development.</t>
+  </si>
+  <si>
+    <t>Arabic, Biotechnology, Botany, Chemistry, Commerce, Computer Applications &amp; Information Technology, Economics, Education, English, Environmental Science, Geography, History, Islamic Studies, Kashmiri, Management Studies, Mathematics, Persian, Philosophy, Physics, Political Science, Psychology, Public Administration, Sociology, Statistics, Urdu, Zoology.</t>
+  </si>
+  <si>
+    <t>Undergraduate, Postgraduate, Integrated and Professional programmes in Arts, Science, Commerce, Management and Computer Applications.</t>
+  </si>
+  <si>
+    <t>Central Library available with digital learning resources.</t>
+  </si>
+  <si>
+    <t>Boys' and Girls' hostels available within the campus.</t>
+  </si>
+  <si>
+    <t>Well-equipped laboratories for Physical Sciences, Biological Sciences, Computer Applications &amp; IT, Biotechnology and other science disciplines.</t>
+  </si>
+  <si>
+    <t>Indoor and outdoor sports facilities with dedicated playgrounds and sports activities.</t>
+  </si>
+  <si>
+    <t>Smart classrooms, Central Library, Boys' &amp; Girls' Hostels, Computer Labs, Science Laboratories, Auditorium, Seminar Hall, Wi-Fi campus, Canteen, Health Centre, Career Counselling, NCC, NSS, Sports Complex and Green Campus.</t>
+  </si>
+  <si>
+    <t>https://gdcbemina.edu.in</t>
+  </si>
+  <si>
+    <t>https://maps.google.com/?q=Abdul+Ahad+Azad+Memorial+Degree+College+Bemina+Srinagar</t>
+  </si>
+  <si>
+    <t>gdcbemina@gmail.com</t>
+  </si>
+  <si>
+    <t>AAAMDC Bemina/GDC Bemina</t>
+  </si>
+  <si>
+    <t>GCW M.A. Road</t>
+  </si>
+  <si>
+    <t>M.A. Road, Kothi Bagh, Srinagar – 190001, Jammu &amp; Kashmir</t>
+  </si>
+  <si>
+    <t>Prof. (Dr.) Yasmeen Farooq</t>
+  </si>
+  <si>
+    <t>Government College for Women, M.A. Road is a premier constituent college of Cluster University Srinagar dedicated to women's higher education. The college offers undergraduate, postgraduate, integrated and professional programmes in Arts, Science, Commerce, Computer Applications and Education, with emphasis on academic excellence, research and holistic development.</t>
+  </si>
+  <si>
+    <t>Arabic, Biochemistry, Biotechnology, Botany, Chemistry, Clinical Biochemistry, Commerce, Computer Applications, Economics, Education, English, Environmental Science, Geography, History, Home Science, Islamic Studies, Journalism &amp; Mass Communication, Kashmiri, Mathematics, Music, Persian, Philosophy, Physics, Political Science, Psychology, Sociology, Statistics, Urdu, Zoology.</t>
+  </si>
+  <si>
+    <t>Undergraduate, Postgraduate, Integrated and Professional programmes in Arts, Science, Commerce, Computer Applications, Journalism &amp; Mass Communication and Education.</t>
+  </si>
+  <si>
+    <t>Central Library available.</t>
+  </si>
+  <si>
+    <t>Hostel facility available.</t>
+  </si>
+  <si>
+    <t>Well-equipped laboratories for Science, Computer Applications, Home Science, Clinical Biochemistry, Biotechnology and other practical disciplines.</t>
+  </si>
+  <si>
+    <t>Indoor and outdoor sports facilities available.</t>
+  </si>
+  <si>
+    <t>Smart classrooms, Central Library, Hostel, Science &amp; Computer Laboratories, Seminar Hall, Auditorium, Wi-Fi campus, Canteen, Career Counselling, NCC, NSS and Sports facilities.</t>
+  </si>
+  <si>
+    <t>https://gcwmaroad.edu.in</t>
+  </si>
+  <si>
+    <t>https://maps.google.com/?q=Government+College+for+Women+MA+Road+Srinagar</t>
+  </si>
+  <si>
+    <t>info@gcwmaroad.org</t>
+  </si>
+  <si>
+    <t>Institute of Advanced Studies in Education (Government College of Education)</t>
+  </si>
+  <si>
+    <r>
+      <t>1937</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (as Teacher Training School; upgraded to IASE in 2016)</t>
+    </r>
+  </si>
+  <si>
+    <t>Prof. (Dr.) Seema Naaz</t>
+  </si>
+  <si>
+    <t>Institute of Advanced Studies in Education (IASE), formerly Government College of Education, is the premier teacher education institution in Jammu &amp; Kashmir. Established in 1937 and upgraded to IASE in 2016, it is a constituent college of Cluster University Srinagar offering undergraduate, postgraduate and integrated teacher education programmes with emphasis on quality teaching, educational research and professional development.</t>
+  </si>
+  <si>
+    <t>Education, Teacher Education, Curriculum &amp; Pedagogy, Educational Psychology, Educational Technology, Guidance &amp; Counselling and related teacher education disciplines.</t>
+  </si>
+  <si>
+    <t>B.Ed., M.Ed., Integrated B.A.-B.Ed., Integrated B.Sc.-B.Ed. and Integrated B.Ed.-M.Ed.</t>
+  </si>
+  <si>
+    <t>Psychology Laboratory, Educational Technology Laboratory, ICT &amp; Computer Laboratory, Science Laboratories, Language Laboratory and Teaching-Learning Resource Centre.</t>
+  </si>
+  <si>
+    <t>Central Library, Hostel, ICT-enabled classrooms, Psychology Lab, Educational Technology Lab, Computer Lab, Seminar Hall, Auditorium, Wi-Fi campus, Sports facilities, NCC, NSS and Teacher Education Resource Centre.</t>
+  </si>
+  <si>
+    <t>https://www.gcoekmr.edu.in</t>
+  </si>
+  <si>
+    <t>https://maps.google.com/?q=Institute+of+Advanced+Studies+in+Education+Srinagar</t>
+  </si>
+  <si>
+    <t>principal-iase@jk.gov.in</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +391,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -131,7 +408,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -139,18 +416,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -453,230 +767,519 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20" style="2" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="7" max="7" width="17" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
+    <col min="11" max="11" width="28.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="29.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="24.5703125" style="2" customWidth="1"/>
+    <col min="14" max="15" width="9.140625" style="2"/>
+    <col min="16" max="16" width="12.5703125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="2"/>
+    <col min="18" max="19" width="9.140625" style="4"/>
+    <col min="20" max="21" width="9.140625" style="2"/>
+    <col min="22" max="22" width="12.42578125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="12.28515625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="10">
+        <v>1905</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="390" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
+      <c r="B5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1961</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="115.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>25</v>
+    <row r="6" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="66" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>25</v>
-      </c>
+    <row r="7" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
     </row>
-    <row r="4" spans="1:6" ht="33" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>25</v>
-      </c>
+    <row r="8" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5"/>
     </row>
-    <row r="5" spans="1:6" ht="33" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
+    <row r="9" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5"/>
     </row>
-    <row r="6" spans="1:6" ht="66" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>25</v>
-      </c>
+    <row r="10" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="5"/>
     </row>
-    <row r="7" spans="1:6" ht="33" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
+    <row r="11" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="5"/>
     </row>
-    <row r="8" spans="1:6" ht="66" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="66" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="99" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
+    <row r="12" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3:E12" r:id="rId2" display="https://www.cusrinagar.edu.in/?utm_source=chatgpt.com"/>
+    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="V2" r:id="rId2"/>
+    <hyperlink ref="W2" r:id="rId3"/>
+    <hyperlink ref="U3" r:id="rId4"/>
+    <hyperlink ref="V3" r:id="rId5"/>
+    <hyperlink ref="W3" r:id="rId6"/>
+    <hyperlink ref="U4" r:id="rId7"/>
+    <hyperlink ref="V4" r:id="rId8"/>
+    <hyperlink ref="W4" r:id="rId9"/>
+    <hyperlink ref="U5" r:id="rId10"/>
+    <hyperlink ref="V5" r:id="rId11"/>
+    <hyperlink ref="W5" r:id="rId12"/>
+    <hyperlink ref="U6" r:id="rId13"/>
+    <hyperlink ref="V6" r:id="rId14"/>
+    <hyperlink ref="W6" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
 

--- a/data/official_data/knowledge/colleges.xlsx
+++ b/data/official_data/knowledge/colleges.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="105">
   <si>
     <t>Overview</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>principal-iase@jk.gov.in</t>
+  </si>
+  <si>
+    <t>IASE</t>
   </si>
 </sst>
 </file>
@@ -408,21 +411,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -462,7 +456,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -768,7 +762,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="93" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" style="2" customWidth="1"/>
@@ -792,7 +786,7 @@
     <col min="23" max="23" width="12.28515625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -863,7 +857,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="118.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
@@ -934,7 +928,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="390" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1005,7 +999,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>62</v>
       </c>
@@ -1076,7 +1070,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1147,12 +1141,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>27</v>
@@ -1218,42 +1212,42 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="10"/>
       <c r="C8" s="9"/>
       <c r="D8" s="10"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
